--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:19:25+00:00</t>
+    <t>2026-09-30T09:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,31 +141,31 @@
     <t>staendig</t>
   </si>
   <si>
-    <t>Ständig</t>
+    <t>Always</t>
   </si>
   <si>
     <t>meistens</t>
   </si>
   <si>
-    <t>Meistens</t>
+    <t>Often</t>
   </si>
   <si>
     <t>manchmal</t>
   </si>
   <si>
-    <t>Manchmal</t>
+    <t>Sometimes</t>
   </si>
   <si>
     <t>selten</t>
   </si>
   <si>
-    <t>Selten</t>
+    <t>Rarely</t>
   </si>
   <si>
     <t>nie</t>
   </si>
   <si>
-    <t>Nie</t>
+    <t>Never</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:40:42+00:00</t>
+    <t>2026-09-30T19:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:42:59+00:00</t>
+    <t>2026-09-30T19:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:54:40+00:00</t>
+    <t>2026-10-01T09:59:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T09:59:00+00:00</t>
+    <t>2026-10-01T11:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-haeufigkeit-5.xlsx
+++ b/CodeSystem-dem-haeufigkeit-5.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
